--- a/staff_forms/004_shift_handover_checklist--staff_forms.xlsx
+++ b/staff_forms/004_shift_handover_checklist--staff_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>start_time</t>
+          <t>Start Time</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>end_time</t>
+          <t>End Time</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>staff_handover_details</t>
+          <t>handover_details</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>staff_handover_details</t>
+          <t>Handover Details</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>key_actions</t>
+          <t>actions_taken</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>key_actions</t>
+          <t>Actions Taken</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>handover_issues</t>
+          <t>Handover Issues</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>handover_comments</t>
+          <t>shift_comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>handover_comments</t>
+          <t>Shift Comments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>next_shift</t>
+          <t>Next Shift</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>next_shift</t>
+          <t>end_time_previous_shift</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>next_shift</t>
+          <t>End Time of Previous Shift</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>end_time</t>
+          <t>start_time_previous_shift</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>end_time</t>
+          <t>Start Time of Previous Shift</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>end_time</t>
+          <t>first_shift</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>end_time</t>
+          <t>First Shift</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>report_id</t>
+          <t>Report ID</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -799,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,51 +827,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>key_actions_choices</t>
+          <t>actions_taken_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>action_1</t>
+          <t>completed_task_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Action 1</t>
+          <t>Completed task 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>key_actions_choices</t>
+          <t>actions_taken_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>action_2</t>
+          <t>completed_task_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Action 2</t>
+          <t>Completed task 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>key_actions_choices</t>
+          <t>actions_taken_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>action_3</t>
+          <t>completed_task_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Action 3</t>
+          <t>Completed task 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>actions_taken_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>completed_task_4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Completed task 4</t>
         </is>
       </c>
     </row>
